--- a/backend/users.xlsx
+++ b/backend/users.xlsx
@@ -424,7 +424,7 @@
         <v>admin</v>
       </c>
       <c r="C2" t="str">
-        <v>$2a$10$WfldSqqzr76S2cwjyQ3ipO7QM4Gd5jN9pd5c3FzF7ZO7MhnT5PDJu</v>
+        <v>$2a$10$csg.YpHy6Bm37ha7cUHwB.kC20IpXgmRVlbHbNESjgMM1QZ9OUwBG</v>
       </c>
       <c r="D2" t="str">
         <v>Administrator Desa Kalemago</v>

--- a/backend/users.xlsx
+++ b/backend/users.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,9 +433,26 @@
         <v>admin</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ramasipembuat</v>
+      </c>
+      <c r="C3" t="str">
+        <v>$2a$10$W3SQgKozNORDsDkUl7sFQ.CyNZLAaC0dWhI95b6a6zJkP5FJfSyV2</v>
+      </c>
+      <c r="D3" t="str">
+        <v>developer</v>
+      </c>
+      <c r="E3" t="str">
+        <v>user</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/users.xlsx
+++ b/backend/users.xlsx
@@ -441,13 +441,13 @@
         <v>ramasipembuat</v>
       </c>
       <c r="C3" t="str">
-        <v>$2a$10$W3SQgKozNORDsDkUl7sFQ.CyNZLAaC0dWhI95b6a6zJkP5FJfSyV2</v>
+        <v>$2a$10$cn9z10dzVwj9YA36XksbfunppLP06El2bCHjC1tl9PJiD28iJBaFq</v>
       </c>
       <c r="D3" t="str">
         <v>developer</v>
       </c>
       <c r="E3" t="str">
-        <v>user</v>
+        <v>developer</v>
       </c>
     </row>
   </sheetData>
